--- a/archives/staff/Betatesters/docs/STAFF_Betatesters.xlsx
+++ b/archives/staff/Betatesters/docs/STAFF_Betatesters.xlsx
@@ -89,12 +89,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
@@ -194,7 +194,50 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr" s="3">
+        <is>
+          <t>CZ-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="3">
+        <is>
+          <t>RAFAEL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="3">
+        <is>
+          <t>MENOLASCINA</t>
+        </is>
+      </c>
+      <c r="D3" s="3">
+        <v>04120702370</v>
+      </c>
+      <c r="E3" t="inlineStr" s="3">
+        <is>
+          <t>rafameno@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr" s="3">
+        <is>
+          <t>Betatesters</t>
+        </is>
+      </c>
+      <c r="G3" s="3">
+        <v>9</v>
+      </c>
+      <c r="H3" t="inlineStr" s="3">
+        <is>
+          <t>CZ-001</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr" s="3">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I2"/>
+  <autoFilter ref="A1:I3"/>
 </worksheet>
 </file>